--- a/tables/Table_S5.xlsx
+++ b/tables/Table_S5.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">Gene</t>
   </si>
@@ -32,52 +32,16 @@
     <t xml:space="preserve">HIF1A</t>
   </si>
   <si>
-    <t xml:space="preserve">KDR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMP2</t>
-  </si>
-  <si>
     <t xml:space="preserve">SERPINE1</t>
   </si>
   <si>
     <t xml:space="preserve">BCL2L1</t>
   </si>
   <si>
-    <t xml:space="preserve">ACE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGTR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC2A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDKN1A</t>
   </si>
   <si>
-    <t xml:space="preserve">JAK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCG2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCND2</t>
-  </si>
-  <si>
     <t xml:space="preserve">CASP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FGF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANPEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDNRB</t>
   </si>
 </sst>
 </file>
@@ -453,13 +417,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>1404</v>
+        <v>877</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -467,13 +431,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>793</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -481,13 +445,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>877</v>
+        <v>288</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -495,181 +459,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>793</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="n">
-        <v>767</v>
-      </c>
-      <c r="C8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D8" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="n">
-        <v>763</v>
-      </c>
-      <c r="C9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="n">
-        <v>393</v>
-      </c>
-      <c r="C10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="n">
-        <v>302</v>
-      </c>
-      <c r="C11" t="n">
-        <v>13</v>
-      </c>
-      <c r="D11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="n">
-        <v>288</v>
-      </c>
-      <c r="C12" t="n">
-        <v>9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="n">
-        <v>264</v>
-      </c>
-      <c r="C13" t="n">
         <v>7</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="n">
-        <v>242</v>
-      </c>
-      <c r="C14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" t="n">
-        <v>144</v>
-      </c>
-      <c r="C15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="n">
-        <v>78</v>
-      </c>
-      <c r="C16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" t="n">
-        <v>72</v>
-      </c>
-      <c r="C17" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="n">
-        <v>38</v>
-      </c>
-      <c r="C18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D18" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" t="n">
-        <v>11</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
